--- a/.github/Fuentes de datos/Datos del INE/SDG 2.A.1.2 Valor añadido de la Agricultura como porcentaje del PIB.xlsx
+++ b/.github/Fuentes de datos/Datos del INE/SDG 2.A.1.2 Valor añadido de la Agricultura como porcentaje del PIB.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hop_projects\entorno-dev\L1_STAGE\Datasets_L1_INE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E15F58-B0BA-49D3-9888-6C49594113F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFD576B-6BC3-401B-8F9A-D79091B184F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="31605" windowHeight="18330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6465" yWindow="1185" windowWidth="31485" windowHeight="18330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SDG 2A1 PIB" sheetId="1" r:id="rId1"/>
+    <sheet name="SDG 2A1 PIB" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>2023(A)</t>
   </si>
@@ -106,14 +106,17 @@
     <t>19 Melilla</t>
   </si>
   <si>
-    <t>Autonomia</t>
+    <t xml:space="preserve"> Autonomia</t>
+  </si>
+  <si>
+    <t>Total Nacional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -131,14 +134,6 @@
       <sz val="9"/>
       <color indexed="8"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -293,7 +288,6 @@
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -309,6 +303,7 @@
     <xf numFmtId="4" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,6 +723,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color indexed="9"/>
         </left>
@@ -767,13 +769,6 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -821,19 +816,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52351D4A-602B-40C7-8FE5-83ADA1623735}" name="Tabla1" displayName="Tabla1" ref="A1:J20" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
-  <autoFilter ref="A1:J20" xr:uid="{52351D4A-602B-40C7-8FE5-83ADA1623735}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6DEB8FFB-0323-4175-B394-9FC0E99D5825}" name="Tabla2" displayName="Tabla2" ref="A1:J21" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
+  <autoFilter ref="A1:J21" xr:uid="{37EDB902-8949-49F4-8E68-71EA1A30608D}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{96100DD5-87D4-4A01-896A-F48AD87090A0}" name="Autonomia" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{7B1790EF-B2A1-470B-B3D6-9EE56D53A9FA}" name="2023(A)" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{02927950-1EF8-4783-B7E9-329A03BE0DC3}" name="2022(P)" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{2BC5A2B3-2500-457A-AFDA-8452AE398DDB}" name="2021" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{1F218958-193A-4C1E-8F54-D3CC6CAA93AC}" name="2020" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{3F51D959-8100-4EA0-A7CA-B8727B2474F8}" name="2019" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{FA32AE7E-6CDA-4E14-AF3B-6B87C6F22197}" name="2018" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{142D4289-5BE0-4821-91DD-260A1376D2D9}" name="2017" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{A045E9DC-82D3-4400-8C93-7A12305BEDD6}" name="2016" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{6C0C9459-F24C-4D97-9501-86A580FB2D41}" name="2015" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{7EF42CEB-9E2F-4C2D-B0EB-3230BBBA3FAB}" name=" Autonomia" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{FE763DC7-0409-4B63-8780-8255DD7540AD}" name="2023(A)" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{4EB678DE-490C-4001-87A8-17E275B67244}" name="2022(P)" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{6EB902F0-4EC3-47EB-9216-4DCD76A03B30}" name="2021" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{2B0D94C7-69F7-45C9-A96A-3464379279C3}" name="2020" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{A6B16F34-4C03-43CC-8983-007C5AFDA71B}" name="2019" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{B37B43E4-4779-496A-99DC-E825FC717D41}" name="2018" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{45C2C35B-28AF-4CBA-B7F2-0B1D8716AFA6}" name="2017" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{8FB7CBEE-D5C9-4979-BB04-AED41C95B47D}" name="2016" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{026558C1-AEE3-496B-9A13-B9EF76A801A6}" name="2015" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1155,8 +1150,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B204571-0848-4D69-8A52-33095AC640C0}">
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -1164,642 +1159,674 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1">
-        <v>5.91</v>
+        <v>2.5</v>
       </c>
       <c r="C2" s="1">
-        <v>5.43</v>
+        <v>2.31</v>
       </c>
       <c r="D2" s="1">
-        <v>6.71</v>
+        <v>2.77</v>
       </c>
       <c r="E2" s="1">
-        <v>6.43</v>
+        <v>2.78</v>
       </c>
       <c r="F2" s="1">
-        <v>5.61</v>
+        <v>2.52</v>
       </c>
       <c r="G2" s="1">
-        <v>6.38</v>
+        <v>2.7</v>
       </c>
       <c r="H2" s="1">
-        <v>6.95</v>
+        <v>2.8</v>
       </c>
       <c r="I2" s="1">
-        <v>6.45</v>
+        <v>2.82</v>
       </c>
       <c r="J2" s="3">
-        <v>6.51</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1">
-        <v>5.38</v>
+        <v>5.91</v>
       </c>
       <c r="C3" s="1">
-        <v>4.8099999999999996</v>
+        <v>5.43</v>
       </c>
       <c r="D3" s="1">
-        <v>5.89</v>
+        <v>6.71</v>
       </c>
       <c r="E3" s="1">
-        <v>6.33</v>
+        <v>6.43</v>
       </c>
       <c r="F3" s="1">
-        <v>5.64</v>
+        <v>5.61</v>
       </c>
       <c r="G3" s="1">
-        <v>5.16</v>
+        <v>6.38</v>
       </c>
       <c r="H3" s="1">
-        <v>5.99</v>
+        <v>6.95</v>
       </c>
       <c r="I3" s="1">
-        <v>6.08</v>
+        <v>6.45</v>
       </c>
       <c r="J3" s="3">
-        <v>4.66</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>1.3</v>
+        <v>5.38</v>
       </c>
       <c r="C4" s="1">
-        <v>1.19</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="D4" s="1">
-        <v>1.4</v>
+        <v>5.89</v>
       </c>
       <c r="E4" s="1">
-        <v>1.4</v>
+        <v>6.33</v>
       </c>
       <c r="F4" s="1">
-        <v>1.41</v>
+        <v>5.64</v>
       </c>
       <c r="G4" s="1">
-        <v>1.35</v>
+        <v>5.16</v>
       </c>
       <c r="H4" s="1">
-        <v>1.28</v>
+        <v>5.99</v>
       </c>
       <c r="I4" s="1">
-        <v>1.35</v>
+        <v>6.08</v>
       </c>
       <c r="J4" s="3">
-        <v>1.38</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="C5" s="1">
-        <v>0.39</v>
+        <v>1.19</v>
       </c>
       <c r="D5" s="1">
-        <v>0.52</v>
+        <v>1.4</v>
       </c>
       <c r="E5" s="1">
-        <v>0.56000000000000005</v>
+        <v>1.4</v>
       </c>
       <c r="F5" s="1">
-        <v>0.55000000000000004</v>
+        <v>1.41</v>
       </c>
       <c r="G5" s="1">
-        <v>0.5</v>
+        <v>1.35</v>
       </c>
       <c r="H5" s="1">
-        <v>0.63</v>
+        <v>1.28</v>
       </c>
       <c r="I5" s="1">
-        <v>0.7</v>
+        <v>1.35</v>
       </c>
       <c r="J5" s="3">
-        <v>0.47</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>1.73</v>
+        <v>0.4</v>
       </c>
       <c r="C6" s="1">
-        <v>1.73</v>
+        <v>0.39</v>
       </c>
       <c r="D6" s="1">
-        <v>1.76</v>
+        <v>0.52</v>
       </c>
       <c r="E6" s="1">
-        <v>1.84</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F6" s="1">
-        <v>1.61</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G6" s="1">
-        <v>1.51</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="1">
-        <v>1.59</v>
+        <v>0.63</v>
       </c>
       <c r="I6" s="1">
-        <v>1.35</v>
+        <v>0.7</v>
       </c>
       <c r="J6" s="3">
-        <v>1.36</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="C7" s="1">
-        <v>1.1299999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="D7" s="1">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="E7" s="1">
-        <v>1.23</v>
+        <v>1.84</v>
       </c>
       <c r="F7" s="1">
-        <v>1.1399999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="G7" s="1">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="H7" s="1">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="I7" s="1">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="J7" s="3">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1">
-        <v>5.29</v>
+        <v>1.23</v>
       </c>
       <c r="C8" s="1">
-        <v>4.88</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D8" s="1">
-        <v>5.49</v>
+        <v>1.37</v>
       </c>
       <c r="E8" s="1">
-        <v>5.24</v>
+        <v>1.23</v>
       </c>
       <c r="F8" s="1">
-        <v>4.32</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="G8" s="1">
-        <v>4.79</v>
+        <v>1.48</v>
       </c>
       <c r="H8" s="1">
-        <v>3.34</v>
+        <v>1.52</v>
       </c>
       <c r="I8" s="1">
-        <v>4.99</v>
+        <v>1.48</v>
       </c>
       <c r="J8" s="3">
-        <v>4.4400000000000004</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1">
-        <v>7.44</v>
+        <v>5.29</v>
       </c>
       <c r="C9" s="1">
-        <v>6.91</v>
+        <v>4.88</v>
       </c>
       <c r="D9" s="1">
-        <v>8.17</v>
+        <v>5.49</v>
       </c>
       <c r="E9" s="1">
-        <v>8.7100000000000009</v>
+        <v>5.24</v>
       </c>
       <c r="F9" s="1">
-        <v>7.6</v>
+        <v>4.32</v>
       </c>
       <c r="G9" s="1">
-        <v>8.99</v>
+        <v>4.79</v>
       </c>
       <c r="H9" s="1">
-        <v>8.58</v>
+        <v>3.34</v>
       </c>
       <c r="I9" s="1">
-        <v>8.7799999999999994</v>
+        <v>4.99</v>
       </c>
       <c r="J9" s="3">
-        <v>7.61</v>
+        <v>4.4400000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1">
-        <v>0.78</v>
+        <v>7.44</v>
       </c>
       <c r="C10" s="1">
-        <v>0.72</v>
+        <v>6.91</v>
       </c>
       <c r="D10" s="1">
-        <v>0.98</v>
+        <v>8.17</v>
       </c>
       <c r="E10" s="1">
-        <v>1.1299999999999999</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="F10" s="1">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="G10" s="1">
-        <v>0.97</v>
+        <v>8.99</v>
       </c>
       <c r="H10" s="1">
-        <v>1.06</v>
+        <v>8.58</v>
       </c>
       <c r="I10" s="1">
-        <v>1.02</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="J10" s="3">
-        <v>1.02</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1">
-        <v>1.72</v>
+        <v>0.78</v>
       </c>
       <c r="C11" s="1">
-        <v>1.56</v>
+        <v>0.72</v>
       </c>
       <c r="D11" s="1">
-        <v>1.92</v>
+        <v>0.98</v>
       </c>
       <c r="E11" s="1">
-        <v>2.1800000000000002</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
       <c r="G11" s="1">
-        <v>1.95</v>
+        <v>0.97</v>
       </c>
       <c r="H11" s="1">
-        <v>2.12</v>
+        <v>1.06</v>
       </c>
       <c r="I11" s="1">
-        <v>2.19</v>
+        <v>1.02</v>
       </c>
       <c r="J11" s="3">
-        <v>2.3199999999999998</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1">
-        <v>7.04</v>
+        <v>1.72</v>
       </c>
       <c r="C12" s="1">
-        <v>6.39</v>
+        <v>1.56</v>
       </c>
       <c r="D12" s="1">
-        <v>7.77</v>
+        <v>1.92</v>
       </c>
       <c r="E12" s="1">
-        <v>6.15</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="F12" s="1">
-        <v>7.23</v>
+        <v>1.85</v>
       </c>
       <c r="G12" s="1">
-        <v>8.2799999999999994</v>
+        <v>1.95</v>
       </c>
       <c r="H12" s="1">
-        <v>8.68</v>
+        <v>2.12</v>
       </c>
       <c r="I12" s="1">
-        <v>7.93</v>
+        <v>2.19</v>
       </c>
       <c r="J12" s="3">
-        <v>7.32</v>
+        <v>2.3199999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1">
-        <v>4.53</v>
+        <v>7.04</v>
       </c>
       <c r="C13" s="1">
-        <v>4.17</v>
+        <v>6.39</v>
       </c>
       <c r="D13" s="1">
-        <v>4.49</v>
+        <v>7.77</v>
       </c>
       <c r="E13" s="1">
-        <v>4.4800000000000004</v>
+        <v>6.15</v>
       </c>
       <c r="F13" s="1">
-        <v>4.92</v>
+        <v>7.23</v>
       </c>
       <c r="G13" s="1">
-        <v>4.7699999999999996</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="H13" s="1">
-        <v>5.2</v>
+        <v>8.68</v>
       </c>
       <c r="I13" s="1">
-        <v>5.49</v>
+        <v>7.93</v>
       </c>
       <c r="J13" s="3">
-        <v>5.52</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1">
-        <v>0.06</v>
+        <v>4.53</v>
       </c>
       <c r="C14" s="1">
-        <v>0.05</v>
+        <v>4.17</v>
       </c>
       <c r="D14" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>4.49</v>
       </c>
       <c r="E14" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="F14" s="1">
-        <v>0.06</v>
+        <v>4.92</v>
       </c>
       <c r="G14" s="1">
-        <v>0.08</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="H14" s="1">
-        <v>0.05</v>
+        <v>5.2</v>
       </c>
       <c r="I14" s="1">
-        <v>0.06</v>
+        <v>5.49</v>
       </c>
       <c r="J14" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1">
-        <v>4.16</v>
+        <v>0.06</v>
       </c>
       <c r="C15" s="1">
-        <v>3.91</v>
+        <v>0.05</v>
       </c>
       <c r="D15" s="1">
-        <v>4.68</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E15" s="1">
-        <v>4.93</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F15" s="1">
-        <v>4.97</v>
+        <v>0.06</v>
       </c>
       <c r="G15" s="1">
-        <v>4.7300000000000004</v>
+        <v>0.08</v>
       </c>
       <c r="H15" s="1">
-        <v>5.22</v>
+        <v>0.05</v>
       </c>
       <c r="I15" s="1">
-        <v>5.35</v>
+        <v>0.06</v>
       </c>
       <c r="J15" s="3">
-        <v>5.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1">
-        <v>3.45</v>
+        <v>4.16</v>
       </c>
       <c r="C16" s="1">
-        <v>3.18</v>
+        <v>3.91</v>
       </c>
       <c r="D16" s="1">
-        <v>3.5</v>
+        <v>4.68</v>
       </c>
       <c r="E16" s="1">
-        <v>3.6</v>
+        <v>4.93</v>
       </c>
       <c r="F16" s="1">
-        <v>3.26</v>
+        <v>4.97</v>
       </c>
       <c r="G16" s="1">
-        <v>3.2</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="H16" s="1">
-        <v>3.65</v>
+        <v>5.22</v>
       </c>
       <c r="I16" s="1">
-        <v>3.42</v>
+        <v>5.35</v>
       </c>
       <c r="J16" s="3">
-        <v>3.4</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1">
-        <v>0.56999999999999995</v>
+        <v>3.45</v>
       </c>
       <c r="C17" s="1">
-        <v>0.53</v>
+        <v>3.18</v>
       </c>
       <c r="D17" s="1">
-        <v>0.57999999999999996</v>
+        <v>3.5</v>
       </c>
       <c r="E17" s="1">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="F17" s="1">
-        <v>0.64</v>
+        <v>3.26</v>
       </c>
       <c r="G17" s="1">
-        <v>0.71</v>
+        <v>3.2</v>
       </c>
       <c r="H17" s="1">
-        <v>0.72</v>
+        <v>3.65</v>
       </c>
       <c r="I17" s="1">
-        <v>0.76</v>
+        <v>3.42</v>
       </c>
       <c r="J17" s="3">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1">
-        <v>5.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="C18" s="1">
-        <v>5.08</v>
+        <v>0.53</v>
       </c>
       <c r="D18" s="1">
-        <v>5.54</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="E18" s="1">
-        <v>5.65</v>
+        <v>0.6</v>
       </c>
       <c r="F18" s="1">
-        <v>5.5</v>
+        <v>0.64</v>
       </c>
       <c r="G18" s="1">
-        <v>6.49</v>
+        <v>0.71</v>
       </c>
       <c r="H18" s="1">
-        <v>5.63</v>
+        <v>0.72</v>
       </c>
       <c r="I18" s="1">
-        <v>4.28</v>
+        <v>0.76</v>
       </c>
       <c r="J18" s="3">
-        <v>6.04</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1">
+        <v>5.57</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5.08</v>
+      </c>
+      <c r="D19" s="1">
+        <v>5.54</v>
+      </c>
+      <c r="E19" s="1">
+        <v>5.65</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G19" s="1">
+        <v>6.49</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5.63</v>
+      </c>
+      <c r="I19" s="1">
+        <v>4.28</v>
+      </c>
+      <c r="J19" s="3">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B20" s="1">
         <v>0.09</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C20" s="1">
         <v>0.09</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>0.12</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E20" s="1">
         <v>0.11</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F20" s="1">
         <v>0.11</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G20" s="1">
         <v>0.13</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H20" s="1">
         <v>0.2</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I20" s="1">
         <v>0.18</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J20" s="3">
         <v>0.19</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B21" s="7">
         <v>0.05</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C21" s="7">
         <v>0.05</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D21" s="7">
         <v>0.04</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E21" s="7">
         <v>0.05</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F21" s="7">
         <v>0.04</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G21" s="7">
         <v>0.03</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H21" s="7">
         <v>0.04</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I21" s="7">
         <v>0.05</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J21" s="8">
         <v>0.05</v>
       </c>
     </row>
